--- a/experiments/results/resnet_imagenet34/ImageNet-1K/ASH/standard/results.xlsx
+++ b/experiments/results/resnet_imagenet34/ImageNet-1K/ASH/standard/results.xlsx
@@ -342,7 +342,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="11" max="11"/>
@@ -503,6 +503,80 @@
       <c r="K4" s="4" t="inlineStr">
         <is>
           <t>dice_p=None,ash_p=90,react_th=None,scale_th=None,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>90.01000000000001</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>50.34</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>85.39</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>16.19</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>96.5</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>21.37</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>95.43000000000001</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="J5" s="4" t="n">
+        <v>91.83</v>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=95,react_th=None,scale_th=None,type=avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>38.28</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>91.54000000000001</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>48.75</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>88.77</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>96.43000000000001</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>21.88</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>96.09</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>31.33</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>93.20999999999999</v>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>dice_p=None,ash_p=85,react_th=None,scale_th=None,type=avg</t>
         </is>
       </c>
     </row>
